--- a/GearSage-client/pkgGear/data_raw/keitech_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/keitech_rod_import.xlsx
@@ -446,8 +446,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,7 +518,37 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>series_positioning</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>main_selling_points</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>official_reference_price</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>market_status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>player_positioning</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>player_selling_points</t>
         </is>
       </c>
     </row>
@@ -550,7 +591,7 @@
           <t>2026-04-10T05:56:19.503Z</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>巻き物というと、高活性な魚を手にするための手段だと安易に考えがちです。しかしながら昨今の釣り場環境において、エリアを広く探る展開が有効な状況は明らかに少なくなったと感じます。_x000d_
 キャスト精度の必要性は言わずもがな、ここぞという場所ではトレースコースやレンジを変え、しつこく何度も通してやっと口を遣う場面が多々あるのです。_x000d_
@@ -598,7 +639,7 @@
           <t>2026-04-10T05:56:22.101Z</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>感度とリフトパワーを備え、_x000d_
 なおかつ軽量なノースフォーク_x000d_
@@ -651,7 +692,7 @@
           <t>2026-04-10T05:56:24.964Z</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2019年、わたしたちは7フィート6インチのロッド『ナナロクシリーズ』を発売いたしました。そのレングスはシャローの接近戦を有利に運ぶ絶対解であり、カバー攻略において大きなアドバンテージをもたらします。延々と続くアシをていねいに刻んでいく。複雑なブッシュの奥へそっとリグを送り込む。アタリがあれば力強くフッキングを決め、間髪入れず相手を障害物から引き剥がす…そんな、ブラックバスという魚ならではの釣りの醍醐味が味わえるロッドだと自負しております。_x000d_
 しかし一方で、開発段階から『ナナロクシリーズ』を使い込むほどにパワーゲーム主体の展開だけでは手に負えない状況があることもあらためて実感していました。シンカーを軽くしたり、ルアーのボリュームを落としたうえで、繊細な誘いをかけてみると反応が返ってくるケースがしばしば…そして7フィート6インチという長さが活きる、まったく別の世界があることに気づいたのです。_x000d_
@@ -699,7 +740,7 @@
           <t>2026-04-10T05:56:26.942Z</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>”バスがよく釣れること。”　_x000d_
 我々が釣り道具を創るときのボディコンセプトです。_x000d_
@@ -723,8 +764,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI22"/>
+  <dimension ref="A1:AJ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -894,10 +939,15 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
@@ -972,6 +1022,7 @@
           <t>L</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1042,6 +1093,7 @@
           <t>L+</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1112,6 +1164,7 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1182,6 +1235,7 @@
           <t>M</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1252,6 +1306,7 @@
           <t>MH</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1322,6 +1377,7 @@
           <t>XH</t>
         </is>
       </c>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1392,6 +1448,7 @@
           <t>XH</t>
         </is>
       </c>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1462,6 +1519,7 @@
           <t>L</t>
         </is>
       </c>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1532,6 +1590,7 @@
           <t>L+</t>
         </is>
       </c>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1602,6 +1661,7 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1672,6 +1732,7 @@
           <t>MH</t>
         </is>
       </c>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1742,6 +1803,7 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1812,6 +1874,7 @@
           <t>M</t>
         </is>
       </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1882,6 +1945,7 @@
           <t>MH</t>
         </is>
       </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1952,6 +2016,7 @@
           <t>H</t>
         </is>
       </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2022,6 +2087,7 @@
           <t>XH</t>
         </is>
       </c>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2092,6 +2158,7 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2162,6 +2229,7 @@
           <t>M</t>
         </is>
       </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2232,6 +2300,7 @@
           <t>MH</t>
         </is>
       </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2302,6 +2371,7 @@
           <t>H</t>
         </is>
       </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2372,6 +2442,7 @@
           <t>XH</t>
         </is>
       </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
